--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.82962323795921</v>
+        <v>3.222313776168372</v>
       </c>
       <c r="D2" t="n">
-        <v>12.60945256247919</v>
+        <v>2.049036041402868</v>
       </c>
       <c r="E2" t="n">
-        <v>11.05903819216919</v>
+        <v>1.797093706227493</v>
       </c>
       <c r="F2" t="n">
-        <v>8.814082509637393</v>
+        <v>1.432288407816076</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.10185597081307</v>
+        <v>1.804051595257125</v>
       </c>
       <c r="D3" t="n">
-        <v>8.861366490941595</v>
+        <v>1.439972054778009</v>
       </c>
       <c r="E3" t="n">
-        <v>11.05903819216919</v>
+        <v>1.797093706227493</v>
       </c>
       <c r="F3" t="n">
-        <v>8.814082509637393</v>
+        <v>1.432288407816076</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.79722325528436</v>
+        <v>6.142048778983709</v>
       </c>
       <c r="D4" t="n">
-        <v>23.82442436908651</v>
+        <v>3.871468959976557</v>
       </c>
       <c r="E4" t="n">
-        <v>11.05903819216919</v>
+        <v>1.797093706227493</v>
       </c>
       <c r="F4" t="n">
-        <v>8.814082509637393</v>
+        <v>1.432288407816076</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.17042426412475</v>
+        <v>5.065193942920271</v>
       </c>
       <c r="D5" t="n">
-        <v>31.02312232139216</v>
+        <v>5.041257377226226</v>
       </c>
       <c r="E5" t="n">
-        <v>11.05903819216919</v>
+        <v>1.797093706227493</v>
       </c>
       <c r="F5" t="n">
-        <v>8.814082509637393</v>
+        <v>1.432288407816076</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.60996052110167</v>
+        <v>7.249118584679022</v>
       </c>
       <c r="D6" t="n">
-        <v>32.68604243608123</v>
+        <v>5.3114818958632</v>
       </c>
       <c r="E6" t="n">
-        <v>11.05903819216919</v>
+        <v>1.797093706227493</v>
       </c>
       <c r="F6" t="n">
-        <v>8.814082509637393</v>
+        <v>1.432288407816076</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.99467326150818</v>
+        <v>5.03663440499508</v>
       </c>
       <c r="D7" t="n">
-        <v>18.99010774501296</v>
+        <v>3.085892508564607</v>
       </c>
       <c r="E7" t="n">
-        <v>11.05903819216919</v>
+        <v>1.797093706227493</v>
       </c>
       <c r="F7" t="n">
-        <v>8.814082509637393</v>
+        <v>1.432288407816076</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
